--- a/기획/림버스 컴퍼니/스킬 테이블.xlsx
+++ b/기획/림버스 컴퍼니/스킬 테이블.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\림버스 컴퍼니\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAA46C76-8C99-4EEF-B9D2-4FDA08E2C5D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45CBB14-A9AA-4D9C-9C66-54AE2A7BD998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7800" yWindow="1845" windowWidth="21600" windowHeight="11295" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
+    <workbookView xWindow="3660" yWindow="1935" windowWidth="21600" windowHeight="11295" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t xml:space="preserve">한글명 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,10 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>코인 위력(절대 값)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>코인 타입</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,7 +76,66 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공용 키워드</t>
+    <t>코인 위력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분노 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나태 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색욕 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐식 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호흡 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>침잠 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>질투 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 위력 증가 값_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 위력 증가 조건_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 위력 증가 조건_2</t>
+  </si>
+  <si>
+    <t>코인 위력 증가 값_2</t>
+  </si>
+  <si>
+    <t>코인 위력 증가 조건_3</t>
+  </si>
+  <si>
+    <t>코인 위력 증가 값_3</t>
+  </si>
+  <si>
+    <t>코인 위력 증가 조건_4</t>
+  </si>
+  <si>
+    <t>코인 위력 증가 값_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 위력</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -445,10 +500,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBEBB1C6-45A4-4CCC-B8BB-4A16F0A92775}">
-  <dimension ref="C6:H10"/>
+  <dimension ref="C6:H29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="7.75" bestFit="1" customWidth="1"/>
   </cols>
@@ -475,31 +530,175 @@
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
         <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/기획/림버스 컴퍼니/스킬 테이블.xlsx
+++ b/기획/림버스 컴퍼니/스킬 테이블.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\림버스 컴퍼니\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45CBB14-A9AA-4D9C-9C66-54AE2A7BD998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8DD43B-7E95-4725-94EB-64E0D836A8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="1935" windowWidth="21600" windowHeight="11295" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
+    <workbookView xWindow="5670" yWindow="960" windowWidth="21600" windowHeight="11295" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
   <si>
     <t xml:space="preserve">한글명 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,10 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>코인 타입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,62 +76,127 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>분노 속성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나태 속성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>색욕 속성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탐식 속성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>호흡 속성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>침잠 속성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>질투 속성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 위력 증가 값_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 위력 증가 조건_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 위력 증가 조건_2</t>
-  </si>
-  <si>
-    <t>코인 위력 증가 값_2</t>
-  </si>
-  <si>
-    <t>코인 위력 증가 조건_3</t>
-  </si>
-  <si>
-    <t>코인 위력 증가 값_3</t>
-  </si>
-  <si>
-    <t>코인 위력 증가 조건_4</t>
-  </si>
-  <si>
-    <t>코인 위력 증가 값_4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>기본 위력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>증가량_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 타입_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위력 증가 타입_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위력 조건_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>횟수 조건_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨 타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨 증가량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 대분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 유형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죄악 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 가중치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 효과 키워드 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 효과 키워드 타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 효과 키워드 수치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 효과 조건 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 효과 조건 수치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 효과 조건 타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 효과 조건 ID_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 효과 조건 타입_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 효과 조건 수치_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 효과 키워드 ID_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 효과 키워드 타입_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 효과 키워드 수치_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -182,9 +243,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -500,15 +564,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBEBB1C6-45A4-4CCC-B8BB-4A16F0A92775}">
-  <dimension ref="C6:H29"/>
+  <dimension ref="C6:I44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="7.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="75.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>0</v>
       </c>
@@ -518,187 +583,417 @@
       <c r="E6" t="s">
         <v>2</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
         <v>26</v>
       </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
         <v>6</v>
       </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
         <v>10</v>
       </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C21" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>-9999</v>
+      </c>
+      <c r="H22" s="1">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>-9999</v>
+      </c>
+      <c r="H23" s="1">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C41" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C42" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C43" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C44" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/기획/림버스 컴퍼니/스킬 테이블.xlsx
+++ b/기획/림버스 컴퍼니/스킬 테이블.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\림버스 컴퍼니\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8DD43B-7E95-4725-94EB-64E0D836A8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9193121-729F-44F1-90BE-969D8E8FED04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5670" yWindow="960" windowWidth="21600" windowHeight="11295" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="스킬 ID 규칙" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="69">
   <si>
     <t xml:space="preserve">한글명 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,14 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>최솟 값</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최댓 값</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>코인 개수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -124,10 +119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>레벨 타입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>레벨 증가량</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -197,6 +188,229 @@
   </si>
   <si>
     <t>코인 효과 키워드 수치_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 코인 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>000000</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0000</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>000000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수감자 번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출시 시즌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01-이상,
+02-파우스트,
+03-돈키호테,
+04-료슈,
+05-뫼르소,
+06-홍루,
+07-히스클리프,
+08-이스마엘,
+09-로쟈,
+11-싱클레어,
+12-오티스,
+13-그레고르</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-통상 인격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출시 순서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">0X-패시브 스킬 계통
+5X-서포트 패시브 스킬 계통
+1X-일반 공격 1 스킬 계통
+2X-일반 공격 2 스킬 계통
+3X-일반 공격 3 스킬 계통
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수감자별 해당 인격의
+시즌별 출시 순서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-무속성, 01-분노, 02-색욕, 03-나태, 04-탐식, 05-우울, 06-오만, 07-질투</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-별도 생성 또는 불필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>false-위력, true-횟수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 효과 조건 키워드 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키워드 ID 목록 참조.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 효과 조건 분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-미만, 01-이하, 02-동일, 03-이상, 04-초과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 효과 작용 형태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>false-증가, true-감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스킬 코인 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-일반 코인, 01-파괴 불가 코인, 04-적출 코인, 07-소멸 코인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID_N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 ID 규칙 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0X-패시브 스킬 계통, 5X-서포트 패시브 스킬 계통, 1X-일반 공격 1 스킬 계통, 2X-일반 공격 2 스킬 계통, 3X-일반 공격 3 스킬 계통, 4X-수비 스킬 계통</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-참격, 01-관통, 03-타격, 20-방어, 21-강화 방어, 30-회피, 40-반격, 41-강화 반격</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -204,7 +418,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,6 +431,22 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -243,12 +473,30 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,436 +812,287 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBEBB1C6-45A4-4CCC-B8BB-4A16F0A92775}">
-  <dimension ref="C6:I44"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="7.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="75.625" customWidth="1"/>
+    <col min="1" max="1" width="24.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="3"/>
+    <col min="3" max="3" width="11.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="127.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
+      <c r="E13" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
+      <c r="C17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
+      <c r="D18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>-9999</v>
-      </c>
-      <c r="H22" s="1">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>-9999</v>
-      </c>
-      <c r="H23" s="1">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
+      <c r="E19" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C32" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C34" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C35" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="36" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C36" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C37" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="39" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C39" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C41" t="s">
-        <v>37</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C42" t="s">
-        <v>38</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C43" t="s">
-        <v>39</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C44" t="s">
-        <v>40</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>99</v>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1001,4 +1100,296 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DB2B28-039E-4BD1-B89C-953EDD84E051}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="198" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD34E334-5291-47B3-A268-9B3E716C83AF}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A729FAB-49ED-4FAB-8AC9-4D48204BEB95}">
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="8.125" customWidth="1"/>
+    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="21.5" customWidth="1"/>
+    <col min="19" max="19" width="12.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/기획/림버스 컴퍼니/스킬 테이블.xlsx
+++ b/기획/림버스 컴퍼니/스킬 테이블.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\림버스 컴퍼니\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9193121-729F-44F1-90BE-969D8E8FED04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6423154A-A6EE-4BBD-831D-4D1B11C328FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="스킬 ID 규칙" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="전투 스킬 메인 테이블" sheetId="1" r:id="rId1"/>
+    <sheet name="스킬 메인 효과 테이블" sheetId="6" r:id="rId2"/>
+    <sheet name="스킬 ID 규칙" sheetId="4" r:id="rId3"/>
+    <sheet name="타이밍 조건 ID 규칙" sheetId="5" r:id="rId4"/>
+    <sheet name="코인 효과 테이블" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="102">
   <si>
     <t xml:space="preserve">한글명 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,30 +76,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>증가량_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>null</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 타입_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>위력 증가 타입_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>위력 조건_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>횟수 조건_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬 명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -123,75 +100,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스킬 대분류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬 분류</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격 유형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>죄악 속성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>공격 가중치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 효과 키워드 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 효과 키워드 타입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 효과 키워드 수치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 효과 조건 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 효과 조건 수치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 효과 조건 타입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 효과 조건 ID_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 효과 조건 타입_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 효과 조건 수치_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 효과 키워드 ID_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 효과 키워드 타입_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 효과 키워드 수치_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 코인 ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -358,59 +275,309 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>false-위력, true-횟수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 효과 조건 키워드 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>키워드 ID 목록 참조.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>메인 효과 조건 분류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>00-미만, 01-이하, 02-동일, 03-이상, 04-초과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 효과 작용 형태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>false-증가, true-감소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기본 스킬 코인 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>00-일반 코인, 01-파괴 불가 코인, 04-적출 코인, 07-소멸 코인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 코인 효과 ID_N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 ID 규칙 참조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0X-패시브 스킬 계통, 5X-서포트 패시브 스킬 계통, 1X-일반 공격 1 스킬 계통, 2X-일반 공격 2 스킬 계통, 3X-일반 공격 3 스킬 계통, 4X-수비 스킬 계통</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>00-참격, 01-관통, 03-타격, 20-방어, 21-강화 방어, 30-회피, 40-반격, 41-강화 반격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>false-횟수 또는 미분류, true-위력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세부 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 키워드_1 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 분류_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 키워드_2 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 분류_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 수치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 키워드 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 키워드 타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 작용 형태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-기본 코인, 01-파괴 불가 코인, 04-적출 코인, 07-소멸 코인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 값 제한</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-제한 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-세부 조건 없음,01-합계, 02-차이, 03-또는</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-보유, 01-미보유, 02-미만, 03-이하, 04-동일, 05-이상, 06-초과, 07-N당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st-시작시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ht-적중시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su-성공시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fa-실패시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vc-승리시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>de-패배시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01-전투</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-공격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20-앞면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21-뒷면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31-파괴되지 않고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32-크리티컬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40-회피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50-합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이밍 조건 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이밍 조건 ID 규칙 참조.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 ID 규칙 참조.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 1번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항목명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Group</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv Increase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin Pieces</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Pieces</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin Power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Targeting Number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Timing ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Keyword ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Details Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Keyword ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Keyword Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 키워드 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 분류</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -473,7 +640,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -497,6 +664,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -812,18 +982,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBEBB1C6-45A4-4CCC-B8BB-4A16F0A92775}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3"/>
-    <col min="3" max="3" width="11.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="127.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="2" max="2" width="23.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="3"/>
+    <col min="4" max="4" width="11.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="127.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -831,270 +1002,194 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="B7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="B8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="B10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2">
+      <c r="B11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="2">
+        <v>17</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
+        <v>77</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1103,6 +1198,213 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14839D91-30A9-41E5-AB17-89F8A163A9E9}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DB2B28-039E-4BD1-B89C-953EDD84E051}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1116,194 +1418,44 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="198" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD34E334-5291-47B3-A268-9B3E716C83AF}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1313,83 +1465,340 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A729FAB-49ED-4FAB-8AC9-4D48204BEB95}">
-  <dimension ref="A1:S1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBEC812-F90C-44E3-B962-AD2191B553DE}">
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.125" customWidth="1"/>
-    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="21.5" customWidth="1"/>
-    <col min="19" max="19" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="5.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="13.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="5.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>38</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD34E334-5291-47B3-A268-9B3E716C83AF}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="68.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:A15"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/기획/림버스 컴퍼니/스킬 테이블.xlsx
+++ b/기획/림버스 컴퍼니/스킬 테이블.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\림버스 컴퍼니\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6423154A-A6EE-4BBD-831D-4D1B11C328FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DE0D36-A949-42AA-9BED-66CE53004EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
+    <workbookView xWindow="300" yWindow="735" windowWidth="21600" windowHeight="8670" firstSheet="1" activeTab="2" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
   </bookViews>
   <sheets>
     <sheet name="전투 스킬 메인 테이블" sheetId="1" r:id="rId1"/>
-    <sheet name="스킬 메인 효과 테이블" sheetId="6" r:id="rId2"/>
-    <sheet name="스킬 ID 규칙" sheetId="4" r:id="rId3"/>
-    <sheet name="타이밍 조건 ID 규칙" sheetId="5" r:id="rId4"/>
-    <sheet name="코인 효과 테이블" sheetId="2" r:id="rId5"/>
+    <sheet name="스킬 효과 테이블" sheetId="6" r:id="rId2"/>
+    <sheet name="코인 효과 테이블" sheetId="2" r:id="rId3"/>
+    <sheet name="스킬 ID 규칙" sheetId="4" r:id="rId4"/>
+    <sheet name="타이밍 조건 ID 규칙" sheetId="5" r:id="rId5"/>
+    <sheet name="패시브 스킬 테이블" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="145">
   <si>
     <t xml:space="preserve">한글명 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -429,14 +430,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>00-턴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01-전투</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10-공격</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -465,30 +458,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>타이밍 조건 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타이밍 조건 ID 규칙 참조.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬 ID 규칙 참조.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>코인 1번</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬 코인 효과 ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>항목명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -537,10 +514,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Timing ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Condition Keyword ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -578,6 +551,252 @@
   </si>
   <si>
     <t>조건 분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타임 키워드 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time Keyword ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타임 키워드 ID 규칙 참조.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 효과 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Effect ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>번외 코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 ID 규칙에 번외 코드 확인.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin Effect_1 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 효과_1 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 ID 규칙에 번외 코드 확인 및 해당 항목 증설 가능.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin Number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Keyword_1 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Detail Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Keyword_2 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Group_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Group_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활성화 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-조건 없음, 01-보유, 02-공명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분노 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색욕 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나태 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐식 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우울 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오만 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>질투 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Activation Condition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-활성화 조건 항목(Activation Condition)이 0일 경우.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wrath Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lust Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sloth Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gluttony Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gloom Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pride Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Envy Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 효과 텍스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Effect Text</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>us-사용시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01-턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-전투</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>al-상시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ub-사용전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-보유 및 조건 없음, 01-미보유, 02-미만, 03-이하, 04-동일, 05-이상, 06-초과, 07-N당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 수치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(+)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(+)00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mn-메인
+co-코인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -640,7 +859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -666,6 +885,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -982,19 +1204,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBEBB1C6-45A4-4CCC-B8BB-4A16F0A92775}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="11.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="127.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="3"/>
+    <col min="3" max="3" width="11.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="127.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1002,194 +1223,196 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E2" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="2">
+        <v>76</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2">
+        <v>84</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="2">
+        <v>77</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2">
         <v>0</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="2">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="2">
+        <v>79</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2">
         <v>0</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="2">
+        <v>80</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="2">
+        <v>81</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="2">
+        <v>82</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+        <v>99</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1199,16 +1422,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14839D91-30A9-41E5-AB17-89F8A163A9E9}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.5" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1216,186 +1439,215 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="7" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1405,57 +1657,270 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DB2B28-039E-4BD1-B89C-953EDD84E051}">
-  <dimension ref="A1:D3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD34E334-5291-47B3-A268-9B3E716C83AF}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5" customWidth="1"/>
+    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="198" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>29</v>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1465,8 +1930,88 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DB2B28-039E-4BD1-B89C-953EDD84E051}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="198" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBEC812-F90C-44E3-B962-AD2191B553DE}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.75" style="2" bestFit="1" customWidth="1"/>
@@ -1492,7 +2037,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>58</v>
@@ -1500,7 +2045,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>59</v>
@@ -1508,7 +2053,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>60</v>
@@ -1516,7 +2061,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>61</v>
@@ -1524,7 +2069,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>62</v>
@@ -1532,7 +2077,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>63</v>
@@ -1540,17 +2085,31 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1559,245 +2118,196 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD34E334-5291-47B3-A268-9B3E716C83AF}">
-  <dimension ref="A1:F15"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55016CA4-31C4-4B3F-A4B6-EDEF5B983C20}">
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="68.375" customWidth="1"/>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="139.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="B2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="D13" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:A15"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/기획/림버스 컴퍼니/스킬 테이블.xlsx
+++ b/기획/림버스 컴퍼니/스킬 테이블.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\림버스 컴퍼니\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DE0D36-A949-42AA-9BED-66CE53004EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC01EFEF-87A7-4EB0-B301-46338849B4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="735" windowWidth="21600" windowHeight="8670" firstSheet="1" activeTab="2" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
+    <workbookView xWindow="8070" yWindow="585" windowWidth="20880" windowHeight="11295" tabRatio="796" activeTab="3" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
   </bookViews>
   <sheets>
-    <sheet name="전투 스킬 메인 테이블" sheetId="1" r:id="rId1"/>
-    <sheet name="스킬 효과 테이블" sheetId="6" r:id="rId2"/>
-    <sheet name="코인 효과 테이블" sheetId="2" r:id="rId3"/>
-    <sheet name="스킬 ID 규칙" sheetId="4" r:id="rId4"/>
-    <sheet name="타이밍 조건 ID 규칙" sheetId="5" r:id="rId5"/>
-    <sheet name="패시브 스킬 테이블" sheetId="10" r:id="rId6"/>
+    <sheet name="테이블 링크" sheetId="11" r:id="rId1"/>
+    <sheet name="전투 스킬 메인 테이블" sheetId="1" r:id="rId2"/>
+    <sheet name="스킬 효과 테이블" sheetId="6" r:id="rId3"/>
+    <sheet name="키워드 목록" sheetId="12" r:id="rId4"/>
+    <sheet name="코인 효과 테이블" sheetId="2" r:id="rId5"/>
+    <sheet name="스킬 ID 규칙" sheetId="4" r:id="rId6"/>
+    <sheet name="타이밍 키워드 ID 규칙" sheetId="5" r:id="rId7"/>
+    <sheet name="패시브 스킬 테이블" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="409">
   <si>
     <t xml:space="preserve">한글명 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -364,8 +366,260 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>00</t>
+    <t>스킬 ID 규칙 참조.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 코인 효과 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Group</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv Increase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin Pieces</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Pieces</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin Power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Targeting Number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Coin Effect ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Keyword ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Details Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Keyword ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Keyword Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 키워드 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타임 키워드 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time Keyword ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타임 키워드 ID 규칙 참조.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 효과 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Effect ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 ID 규칙에 번외 코드 확인.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin Number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Keyword_1 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Detail Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Keyword_2 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Group_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Group_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활성화 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-조건 없음, 01-보유, 02-공명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분노 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색욕 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나태 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐식 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우울 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오만 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>질투 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Activation Condition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-활성화 조건 항목(Activation Condition)이 0일 경우.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wrath Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lust Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sloth Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gluttony Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gloom Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pride Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Envy Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 효과 텍스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Effect Text</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-보유 및 조건 없음, 01-미보유, 02-미만, 03-이하, 04-동일, 05-이상, 06-초과, 07-N당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 수치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(+)</t>
     </r>
     <r>
       <rPr>
@@ -378,9 +632,23 @@
       </rPr>
       <t>00</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(+)00</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -392,411 +660,1425 @@
       </rPr>
       <t>00</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st-시작시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ht-적중시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>su-성공시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fa-실패시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vc-승리시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>de-패배시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-공격</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20-앞면</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>21-뒷면</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>31-파괴되지 않고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>32-크리티컬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>40-회피</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50-합</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 ID 규칙 참조.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 코인 효과 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill Group</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv Increase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coin Pieces</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill Pieces</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Power</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coin Power</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Targeting Number</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill Coin Effect ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Keyword ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Details Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result Keyword ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result Keyword Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result Limit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조건 키워드 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조건 분류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타임 키워드 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Time Keyword ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타임 키워드 ID 규칙 참조.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 효과 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill Effect ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>번외 코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 ID 규칙에 번외 코드 확인.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coin Effect_1 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 효과_1 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 ID 규칙에 번외 코드 확인 및 해당 항목 증설 가능.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coin Number</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coin Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Keyword_1 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Detail Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Keyword_2 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Group_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Group_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>활성화 조건</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>00-조건 없음, 01-보유, 02-공명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>분노 개수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>색욕 개수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나태 개수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탐식 개수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>우울 개수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오만 개수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>질투 개수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Activation Condition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>00-활성화 조건 항목(Activation Condition)이 0일 경우.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wrath Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lust Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sloth Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gluttony Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gloom Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pride Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Envy Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 효과 텍스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill Effect Text</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>us-사용시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>00-없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01-턴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>02-전투</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>al-상시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ub-사용전</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>00-보유 및 조건 없음, 01-미보유, 02-미만, 03-이하, 04-동일, 05-이상, 06-초과, 07-N당</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>결과 수치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mX-메인 효과
+cX-코인 효과
+X=순서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>번외 코드(메인 테이블 사용 X)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 효과_1 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 코인 효과_1 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Effect_1 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Coin Effect_1 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분류</t>
+  </si>
+  <si>
+    <t>발동 타이밍</t>
+  </si>
+  <si>
+    <t>주요 특징 및 효과 예시</t>
+  </si>
+  <si>
+    <t>전투 준비</t>
+  </si>
+  <si>
+    <t>전투 시작 시</t>
+  </si>
+  <si>
+    <t>스테이지 진입 직후 발동 (에고 기프트, 패시브 등)</t>
+  </si>
+  <si>
+    <t>라운드 시작 시</t>
+  </si>
+  <si>
+    <t>매 턴 시작 시 속도 부여, 버프 수급</t>
+  </si>
+  <si>
+    <t>스킬 사용 시</t>
+  </si>
+  <si>
+    <t>코인을 던지기 전, 스킬을 확정했을 때 발동 (자원 소모 등)</t>
+  </si>
+  <si>
+    <t>합(Clash)</t>
+  </si>
+  <si>
+    <t>합 개시 시</t>
+  </si>
+  <si>
+    <t>적과 합이 성립되는 순간 발동 (합 위력 증가 등)</t>
+  </si>
+  <si>
+    <t>합 승리 시</t>
+  </si>
+  <si>
+    <t>합에서 이겼을 때 발동 (정신력 회복, 다음 코인 강화 등)</t>
+  </si>
+  <si>
+    <t>합 패배 시</t>
+  </si>
+  <si>
+    <t>합에서 졌을 때 발동 (피해량 감소, 반격 준비 등)</t>
+  </si>
+  <si>
+    <t>공격 진행</t>
+  </si>
+  <si>
+    <t>공격 전</t>
+  </si>
+  <si>
+    <t>코인을 던지기 직전에 수치를 보정</t>
+  </si>
+  <si>
+    <t>코인 적중 시</t>
+  </si>
+  <si>
+    <t>각 코인이 적에게 맞았을 때 발동 (디버프 부여)</t>
+  </si>
+  <si>
+    <t>코인 결과(앞/뒤)에 따라 차별화된 효과 발동</t>
+  </si>
+  <si>
+    <t>결과 발생</t>
+  </si>
+  <si>
+    <t>최종 대미지를 높이거나 대미지 후 추가 피해 부여</t>
+  </si>
+  <si>
+    <t>적중 시 (On Hit)</t>
+  </si>
+  <si>
+    <t>공격이 명중했을 때 발동 (가장 일반적인 조건)</t>
+  </si>
+  <si>
+    <t>처치 시</t>
+  </si>
+  <si>
+    <t>해당 공격으로 적을 사망시켰을 때 발동 (정신력 크게 회복)</t>
+  </si>
+  <si>
+    <t>상태 변화</t>
+  </si>
+  <si>
+    <t>피격 시</t>
+  </si>
+  <si>
+    <t>적에게 맞았을 때 발동 (반격, 보호막 등)</t>
+  </si>
+  <si>
+    <t>흐트러짐 시</t>
+  </si>
+  <si>
+    <t>대상이 흐트러질 때 발동되는 추가 효과</t>
+  </si>
+  <si>
+    <t>턴 종료</t>
+  </si>
+  <si>
+    <t>턴 종료 시</t>
+  </si>
+  <si>
+    <t>모든 행동 종료 후 발동 (상태 이상 대미지 계산, 버프 소멸)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(+)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
+      </rPr>
+      <t>앞면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      </rPr>
+      <t>적중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(+)00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mn-메인
-co-코인</t>
+      </rPr>
+      <t>뒷면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cldf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>akaf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coht</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frht</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bkht</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피해량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피해량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dcaf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dcbf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onht</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kltg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obht</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ostg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tued</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도발치</t>
+  </si>
+  <si>
+    <t>키워드</t>
+  </si>
+  <si>
+    <t>위력 및 합</t>
+  </si>
+  <si>
+    <t>마비</t>
+  </si>
+  <si>
+    <t>피해량</t>
+  </si>
+  <si>
+    <t>받는 피해량이 수치에 비례하여 증가/감소 (최대 10)</t>
+  </si>
+  <si>
+    <t>피해량 증가/감소</t>
+  </si>
+  <si>
+    <t>속성/유형 증감</t>
+  </si>
+  <si>
+    <t>특정 공격 유형이나 죄악 속성에 대한 피해량/취약/보호 적용</t>
+  </si>
+  <si>
+    <t>약점 공격 피해</t>
+  </si>
+  <si>
+    <t>적의 약점을 공격할 때 가하는 피해량이 수치에 비례해 증가</t>
+  </si>
+  <si>
+    <t>기동/유틸</t>
+  </si>
+  <si>
+    <t>신속 / 속박</t>
+  </si>
+  <si>
+    <t>집중 전투에서 수치가 높을수록 적에게 공격받을 확률 증가</t>
+  </si>
+  <si>
+    <t>회복 효율 증감</t>
+  </si>
+  <si>
+    <t>상태 제어</t>
+  </si>
+  <si>
+    <t>행동 불가</t>
+  </si>
+  <si>
+    <t>1턴 동안 어떤 행동도 할 수 없음</t>
+  </si>
+  <si>
+    <t>E.G.O 침식</t>
+  </si>
+  <si>
+    <t>특수 코인</t>
+  </si>
+  <si>
+    <t>파괴 불가 코인</t>
+  </si>
+  <si>
+    <t>합 패배 시에도 코인이 유지되며, 피격 후 반격 (패배 시 위력 1 고정)</t>
+  </si>
+  <si>
+    <t>적출 코인</t>
+  </si>
+  <si>
+    <t>광역 난사</t>
+  </si>
+  <si>
+    <t>첫 코인 외에는 대상 중 무작위로 타격 (엄숙한 애도 메커니즘)</t>
+  </si>
+  <si>
+    <t>특수 가드</t>
+  </si>
+  <si>
+    <t>합 가능 가드</t>
+  </si>
+  <si>
+    <t>승리 시 흐트러짐 손상을 주고, 패배 시 상대의 위력을 깎으며 방어</t>
+  </si>
+  <si>
+    <t>화상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출혈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>침잠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호흡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주요 효과 및 메커니즘</t>
+  </si>
+  <si>
+    <t>관련 인격/E.G.O (예시)</t>
+  </si>
+  <si>
+    <t>자원 및 관리</t>
+  </si>
+  <si>
+    <t>탄환 / 재장전</t>
+  </si>
+  <si>
+    <t>특정 스킬 사용 시 소모, 고갈 시 공격 취소 / 탄환 풀 충전</t>
+  </si>
+  <si>
+    <t>R사, LCCB, 마침표 사무소 등</t>
+  </si>
+  <si>
+    <t>E.G.O 자원 획득량+</t>
+  </si>
+  <si>
+    <t>스킬 사용 시 획득하는 자원 수 수치만큼 증가</t>
+  </si>
+  <si>
+    <t>평생 스튜, 소다</t>
+  </si>
+  <si>
+    <t>특수 스택</t>
+  </si>
+  <si>
+    <t>충전 역장 / 고전압 외피</t>
+  </si>
+  <si>
+    <t>(수치×n)만큼 보호막 획득, 소멸 시 충전 획득</t>
+  </si>
+  <si>
+    <t>W사, AEDD 그레고르</t>
+  </si>
+  <si>
+    <t>혈찬 / 누적 혈찬</t>
+  </si>
+  <si>
+    <t>출혈 피해 저장 및 공유, 특정 수치 소모 시 스킬 강화</t>
+  </si>
+  <si>
+    <t>라만차랜드 혈귀 인격들</t>
+  </si>
+  <si>
+    <t>딜리버리 캐리어</t>
+  </si>
+  <si>
+    <t>스택에 따라 속도, 합 위력 증가 (30 이상 시 자해 피해)</t>
+  </si>
+  <si>
+    <t>북부 제뱌찌 협회</t>
+  </si>
+  <si>
+    <t>디버프 (턴 종료)</t>
+  </si>
+  <si>
+    <t>구더기 / 저주</t>
+  </si>
+  <si>
+    <t>탐식 피해 및 출혈 증가 / 다음 턴 무작위 능력치 감소</t>
+  </si>
+  <si>
+    <t>눈속임, 저주못, 지난 날</t>
+  </si>
+  <si>
+    <t>차원 균열 / 올가미</t>
+  </si>
+  <si>
+    <t>턴 종료 시 파열 횟수 증가 / 속도 비례 파열 위력 획득</t>
+  </si>
+  <si>
+    <t>W사 이상, 차원찢개, 올가미</t>
+  </si>
+  <si>
+    <t>주살(신속/독)</t>
+  </si>
+  <si>
+    <t>특정 조건(파열, 크리티컬) 시 수치 감소하며 큰 피해</t>
+  </si>
+  <si>
+    <t>흑수(묘, 사, 유) 시리즈</t>
+  </si>
+  <si>
+    <t>전투 유틸리티</t>
+  </si>
+  <si>
+    <t>결투 선포</t>
+  </si>
+  <si>
+    <t>지정 대상과 합 진행 시 위력 및 신속 증가</t>
+  </si>
+  <si>
+    <t>남부 섕크 협회</t>
+  </si>
+  <si>
+    <t>약점 분석</t>
+  </si>
+  <si>
+    <t>무작위 내성(견딤/보통)을 취약하게 변경 [x-0.2]</t>
+  </si>
+  <si>
+    <t>남부 세븐 협회</t>
+  </si>
+  <si>
+    <t>광신</t>
+  </si>
+  <si>
+    <t>'못'이 부여된 대상 공격 시 최종 위력 증가</t>
+  </si>
+  <si>
+    <t>N사 광신도 인격들</t>
+  </si>
+  <si>
+    <t>스킬 제어</t>
+  </si>
+  <si>
+    <t>버림 / 탐구한 지식</t>
+  </si>
+  <si>
+    <t>스킬 패널에서 스킬 제거 / 마지막에 버린 스킬 등급 저장</t>
+  </si>
+  <si>
+    <t>디에치 협회, 어금니 사무소</t>
+  </si>
+  <si>
+    <t>시간 대여 / 유예</t>
+  </si>
+  <si>
+    <t>다음 턴 강력한 버프 후 속박 / 피해 저장 후 나태 폭발</t>
+  </si>
+  <si>
+    <t>T사 징수직 인격들</t>
+  </si>
+  <si>
+    <t>전략적 휴식 / 전장 퇴각</t>
+  </si>
+  <si>
+    <t>흐트러짐 해제 후 이탈, 대기 인원과 교체 (연속 전투)</t>
+  </si>
+  <si>
+    <t>제뱌찌 로쟈, H사 이스마엘 등</t>
+  </si>
+  <si>
+    <t>특정 인격 전용</t>
+  </si>
+  <si>
+    <t>마탄 / 찢어진 추억</t>
+  </si>
+  <si>
+    <t>수치에 따라 기본/코인 위력 증가 및 스킬 강화</t>
+  </si>
+  <si>
+    <t>마탄 오티스, 흉탄 이상</t>
+  </si>
+  <si>
+    <t>경멸의 시선 / 시선의 경멸</t>
+  </si>
+  <si>
+    <t>피해량 증가 / 7 중첩 시 강력한 보호 및 도발치 획득</t>
+  </si>
+  <si>
+    <t>경멸·경외 료슈</t>
+  </si>
+  <si>
+    <t>마법소녀 / 역변 / 히스테리</t>
+  </si>
+  <si>
+    <t>더하기/빼기 코인 전환 및 정신력 상태에 따른 변화</t>
+  </si>
+  <si>
+    <t>사랑과 증오의 이름 돈키호테</t>
+  </si>
+  <si>
+    <t>단체/조직 특성</t>
+  </si>
+  <si>
+    <t>지령(표식/가호/해금/카르마)</t>
+  </si>
+  <si>
+    <t>특정 조건(지령) 수행 시 '해금' 단계 상승 및 능력치 강화</t>
+  </si>
+  <si>
+    <t>검지(이상, 파우스트 등)</t>
+  </si>
+  <si>
+    <t>임전 / 흑운도</t>
+  </si>
+  <si>
+    <t>출혈 부여량 증가, 참격 위력 및 피해량 대폭 강화</t>
+  </si>
+  <si>
+    <t>흑운회 인격들</t>
+  </si>
+  <si>
+    <t>영감 / 그림 재료</t>
+  </si>
+  <si>
+    <t>특정 상태 적 공격 시 피해량 증가</t>
+  </si>
+  <si>
+    <t>약지(지원 기프트)</t>
+  </si>
+  <si>
+    <t>선율 / 찢긴 색채</t>
+  </si>
+  <si>
+    <t>합 위력 및 피해량 증가 / 피격 시 출혈 부여</t>
+  </si>
+  <si>
+    <t>약지(홍루, 파우스트, 로쟈 등)</t>
+  </si>
+  <si>
+    <t>기타 특수</t>
+  </si>
+  <si>
+    <t>저택의 메아리</t>
+  </si>
+  <si>
+    <t>침잠 횟수 증가 확률 부여, 패닉 유형 강제 변경</t>
+  </si>
+  <si>
+    <t>워더링하이츠 버틀러</t>
+  </si>
+  <si>
+    <t>오혈</t>
+  </si>
+  <si>
+    <t>턴 종료 시 대량의 체력 피해 (자살 기믹)</t>
+  </si>
+  <si>
+    <t>H사 홍원 군주 홍루</t>
+  </si>
+  <si>
+    <t>분홍 꽃잎</t>
+  </si>
+  <si>
+    <t>수치당 우울 취약, 진동 폭발 시 추가 피해</t>
+  </si>
+  <si>
+    <t>분홍 꽃잎 기프트</t>
+  </si>
+  <si>
+    <t>생존 및 사망</t>
+  </si>
+  <si>
+    <t>시술 / 마지막 개조</t>
+  </si>
+  <si>
+    <t>나사빠진 일격(뫼르소)</t>
+  </si>
+  <si>
+    <t>K사 앰플</t>
+  </si>
+  <si>
+    <t>K사 적출직 홍루</t>
+  </si>
+  <si>
+    <t>불허 / 매화첨 / 오혈</t>
+  </si>
+  <si>
+    <t>체력 0에서 1턴 생존(불사) 후 사망 / 강력한 자해 및 공격 버프</t>
+  </si>
+  <si>
+    <t>홍원 군주 홍루, 오혈읍루</t>
+  </si>
+  <si>
+    <t>와일드헌트 / 관</t>
+  </si>
+  <si>
+    <t>사망 시 자원 획득 및 부활 후 재사망 / 침잠 및 합 위력 강화</t>
+  </si>
+  <si>
+    <t>와일드헌트 히스클리프</t>
+  </si>
+  <si>
+    <t>공격 지원</t>
+  </si>
+  <si>
+    <t>원호 공격 / 타겟 포착</t>
+  </si>
+  <si>
+    <t>피쿼드 이스, 마침표 홍루</t>
+  </si>
+  <si>
+    <t>존명 / 뜻에 따라...</t>
+  </si>
+  <si>
+    <t>아군 공격 종료 시 특정 스킬로 추가 지원 공격</t>
+  </si>
+  <si>
+    <t>홍원 군주 홍루 등</t>
+  </si>
+  <si>
+    <t>원호 방어 / 방어 태세</t>
+  </si>
+  <si>
+    <t>아군 대신 타겟이 되어 방어 / 합 승리 시 진동 폭발 및 도발</t>
+  </si>
+  <si>
+    <t>흑수 파우스트, 츠바이 이스</t>
+  </si>
+  <si>
+    <t>특수 상태 이상</t>
+  </si>
+  <si>
+    <t>침잠쇄도</t>
+  </si>
+  <si>
+    <t>개화 E.G.O 동백 이상</t>
+  </si>
+  <si>
+    <t>부적</t>
+  </si>
+  <si>
+    <t>홍적 싱클레어</t>
+  </si>
+  <si>
+    <t>상처 / 깊은 상처</t>
+  </si>
+  <si>
+    <t>밤의 송곳 그레고르</t>
+  </si>
+  <si>
+    <t>포자 / 지네 독</t>
+  </si>
+  <si>
+    <t>턴 종료 시 화상/방레감 부여 및 탐식 피해 / 사망 시 전이</t>
+  </si>
+  <si>
+    <t>호넷 뫼르소, 즉저살 이스</t>
+  </si>
+  <si>
+    <t>인격 고유 기믹</t>
+  </si>
+  <si>
+    <t>가호 / 절망 / 검</t>
+  </si>
+  <si>
+    <t>눈물로 벼려낸 검 로쟈</t>
+  </si>
+  <si>
+    <t>특정 조건(쪽지/단말기) 수행 시 가호 획득 및 성능 단계별 개방</t>
+  </si>
+  <si>
+    <t>호흡 수치에 따라 코인 위력 및 크리티컬 피해량 대폭 증가</t>
+  </si>
+  <si>
+    <t>검계 뫼르소</t>
+  </si>
+  <si>
+    <t>예술(색채/재료)</t>
+  </si>
+  <si>
+    <t>생체 재료 수치에 따라 위력 강화 및 출혈/침잠 복합 시너지</t>
+  </si>
+  <si>
+    <t>약지(홍루, 로쟈 등)</t>
+  </si>
+  <si>
+    <t>특수 탄환(산나비, 포자 등) 관리 / 수치별 가중치 및 효과 변화</t>
+  </si>
+  <si>
+    <t>엄숙한 애도, 마탄 오티스</t>
+  </si>
+  <si>
+    <t>유틸리티/버프</t>
+  </si>
+  <si>
+    <t>흐트러짐 면역 상태로 강력한 원거리 저격 준비</t>
+  </si>
+  <si>
+    <t>동부 시 협회 파우스트</t>
+  </si>
+  <si>
+    <t>과충전</t>
+  </si>
+  <si>
+    <t>행동 불가 상태가 되는 대신 대량의 충전과 방어막/버프 획득</t>
+  </si>
+  <si>
+    <t>W사 히스클리프</t>
+  </si>
+  <si>
+    <t>적의 패닉 유형 변경 및 침잠/화상 비례 피해량 증가</t>
+  </si>
+  <si>
+    <t>램프 그레고르</t>
+  </si>
+  <si>
+    <t>질투/충전 스킬 피해 증폭 및 불사/충전 횟수 획득</t>
+  </si>
+  <si>
+    <t>AEDD 그레고르</t>
+  </si>
+  <si>
+    <t>특수 보조</t>
+  </si>
+  <si>
+    <t>트라우마 방지장</t>
+  </si>
+  <si>
+    <t>정신력 및 침잠 피해 80% 감소</t>
+  </si>
+  <si>
+    <t>기프트 (트라우마 방지장)</t>
+  </si>
+  <si>
+    <t>초정밀 시간 가속</t>
+  </si>
+  <si>
+    <t>진동 폭발 시 흐트러짐 손상 및 피해량 대폭 증가</t>
+  </si>
+  <si>
+    <t>기프트 (시간 가속 장치)</t>
+  </si>
+  <si>
+    <t>아군 전체 충전 소모량에 비례해 공격 레벨 및 피해량 강화</t>
+  </si>
+  <si>
+    <t>기프트 (영구기관 등)</t>
+  </si>
+  <si>
+    <t>한 턴 동안 수치만큼 코인 위력을 0으로 고정</t>
+  </si>
+  <si>
+    <t>스킬의 최종 위력이 수치만큼 증가/감소 (공격/수비/합 전용 존재)</t>
+  </si>
+  <si>
+    <t>더하기 또는 빼기 코인의 위력이 수치만큼 증가/감소</t>
+  </si>
+  <si>
+    <t>공격 또는 방어 레벨이 수치에 비례하여 증가/감소</t>
+  </si>
+  <si>
+    <t>가하는 피해량이 수치당 10%씩 증가/감소 (최대 10)</t>
+  </si>
+  <si>
+    <t>한 턴 동안 속도가 수치만큼 증가/감소</t>
+  </si>
+  <si>
+    <t>정신력 회복량 또는 체력 회복 효율(±10%)을 조절</t>
+  </si>
+  <si>
+    <t>명령 불가 상태가 되며, 침식 스킬만 무작위로 사용</t>
+  </si>
+  <si>
+    <t>상대의 파괴 불가 코인을 파괴할 수 있는 특수한 파괴 불가 코인</t>
+  </si>
+  <si>
+    <t>수치당 피해량·신속 증가 / 5 중첩 시 또는 3턴 뒤 즉사</t>
+  </si>
+  <si>
+    <t>턴 시작 시 체력 회복 / 4 중첩 시 즉사</t>
+  </si>
+  <si>
+    <t>아군 공격 종료 시 자신의 1, 2스킬로 추가 일방 공격</t>
+  </si>
+  <si>
+    <t>(위력×횟수)만큼 정신 피해 폭발 (정신력 없으면 우울 피해)</t>
+  </si>
+  <si>
+    <t>파열 부여 및 획득 시너지 / 6 중첩 시 자폭 피해</t>
+  </si>
+  <si>
+    <t>진동 폭발 시 출혈 횟수 증가 및 속박 부여</t>
+  </si>
+  <si>
+    <t>정신력에 따라 더하기/빼기 코인 스킬 전환 및 도발치 조절</t>
+  </si>
+  <si>
+    <t>역할 분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공용 키워드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 키워드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범용 키워드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고유 키워드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디버프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진동 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>키워드</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> ID</t>
+    </r>
+  </si>
+  <si>
+    <t>위력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강화</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약화</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>레벨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>레벨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>취약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초아광축전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공진</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>충전</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전하침</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>램프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현혹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조준</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자세</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마탄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재장전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자법</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본국검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해금</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지령</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -804,7 +2086,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -836,6 +2118,65 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -845,12 +2186,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -859,7 +2215,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -889,6 +2245,57 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1203,6 +2610,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A58AF3-DFBE-42DA-94BA-1C8D3714BF72}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBEBB1C6-45A4-4CCC-B8BB-4A16F0A92775}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1237,13 +2742,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1251,7 +2756,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
@@ -1265,7 +2770,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -1282,7 +2787,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
@@ -1296,7 +2801,7 @@
         <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
@@ -1313,7 +2818,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>5</v>
@@ -1330,7 +2835,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>5</v>
@@ -1344,7 +2849,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>5</v>
@@ -1361,7 +2866,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>5</v>
@@ -1375,7 +2880,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>5</v>
@@ -1389,7 +2894,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>5</v>
@@ -1399,18 +2904,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>102</v>
-      </c>
+      <c r="E13" s="7"/>
     </row>
     <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -1420,9 +2914,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14839D91-30A9-41E5-AB17-89F8A163A9E9}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -1450,205 +2944,211 @@
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="7" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="7" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2" t="b">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="E6" s="7" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>139</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="7"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="7" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="2">
-        <v>0</v>
+      <c r="D9" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>39</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
       <c r="E11" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="7"/>
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="7" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>105</v>
-      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="E16" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1656,7 +3156,1630 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06EC02D0-4C2D-408B-8AFB-DBB6E17830DA}">
+  <dimension ref="A1:F119"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="19" customWidth="1"/>
+    <col min="4" max="4" width="26.5" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.25" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.625" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="23"/>
+      <c r="D12" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="F12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="26" t="s">
+        <v>389</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="F14" s="21"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="D16" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="F16" s="21"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="F18" s="21"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="F20" s="21"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F22" s="21"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="23"/>
+      <c r="D24" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="23"/>
+      <c r="D25" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="F25" s="21"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C27" s="23"/>
+      <c r="D27" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" s="21"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="23"/>
+      <c r="D28" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="F28" s="21"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="23"/>
+      <c r="D29" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="F29" s="21"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="F30" s="21"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="23"/>
+      <c r="D38" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="C39" s="23"/>
+      <c r="D39" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="C41" s="23"/>
+      <c r="D41" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="23"/>
+      <c r="D43" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="C44" s="23"/>
+      <c r="D44" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="C46" s="23"/>
+      <c r="D46" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="C48" s="23"/>
+      <c r="D48" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C49" s="23"/>
+      <c r="D49" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C50" s="23"/>
+      <c r="D50" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C51" s="23"/>
+      <c r="D51" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="C52" s="23"/>
+      <c r="D52" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="C54" s="23"/>
+      <c r="D54" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="C56" s="23"/>
+      <c r="D56" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="C58" s="23"/>
+      <c r="D58" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="C60" s="23"/>
+      <c r="D60" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B61" s="23"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="C62" s="23"/>
+      <c r="D62" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B64" s="23"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C65" s="23"/>
+      <c r="D65" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B66" s="23"/>
+      <c r="C66" s="23"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B68" s="23"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C69" s="23"/>
+      <c r="D69" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="E69" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B70" s="23"/>
+      <c r="C70" s="23"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B71" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C71" s="23"/>
+      <c r="D71" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B72" s="23"/>
+      <c r="C72" s="23"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B73" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C73" s="23"/>
+      <c r="D73" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="F73" s="21" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B74" s="23"/>
+      <c r="C74" s="23"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B75" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C75" s="23"/>
+      <c r="D75" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="E75" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="F75" s="21" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B76" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C76" s="23"/>
+      <c r="D76" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B77" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C77" s="23"/>
+      <c r="D77" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="F77" s="21" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B78" s="23"/>
+      <c r="C78" s="23"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B79" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C79" s="23"/>
+      <c r="D79" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="E79" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B80" s="23"/>
+      <c r="C80" s="23"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B81" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C81" s="23"/>
+      <c r="D81" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="E81" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="F81" s="21" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B82" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C82" s="23"/>
+      <c r="D82" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="E82" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="F82" s="21" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B83" s="23"/>
+      <c r="C83" s="23"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="21"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B84" s="23"/>
+      <c r="C84" s="23"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="21"/>
+      <c r="F84" s="21"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B85" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C85" s="23"/>
+      <c r="D85" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="E85" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="F85" s="21" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B86" s="23"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="21"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B87" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="C87" s="23"/>
+      <c r="D87" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="E87" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="F87" s="21" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="21"/>
+      <c r="F88" s="21"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B89" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="C89" s="23"/>
+      <c r="D89" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="E89" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="F89" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B90" s="23"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="21"/>
+      <c r="F90" s="21"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B91" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="C91" s="23"/>
+      <c r="D91" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="F91" s="21" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="21"/>
+      <c r="F92" s="21"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B93" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="C93" s="23"/>
+      <c r="D93" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="E93" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F93" s="21" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B94" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="C94" s="23"/>
+      <c r="D94" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E94" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="F94" s="21" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B95" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="C95" s="23"/>
+      <c r="D95" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E95" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="F95" s="21" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B96" s="23"/>
+      <c r="C96" s="23"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="21"/>
+      <c r="F96" s="21"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B97" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="C97" s="23"/>
+      <c r="D97" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="E97" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="F97" s="21" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B98" s="23"/>
+      <c r="C98" s="23"/>
+      <c r="D98" s="21"/>
+      <c r="E98" s="21"/>
+      <c r="F98" s="21"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B99" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C99" s="23"/>
+      <c r="D99" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="E99" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="F99" s="21" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B100" s="23"/>
+      <c r="C100" s="23"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="21"/>
+      <c r="F100" s="21"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B101" s="23"/>
+      <c r="C101" s="23"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="21"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B102" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C102" s="23"/>
+      <c r="D102" s="25" t="s">
+        <v>408</v>
+      </c>
+      <c r="E102" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="F102" s="21" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B103" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C103" s="23"/>
+      <c r="D103" s="25" t="s">
+        <v>407</v>
+      </c>
+      <c r="E103" s="21"/>
+      <c r="F103" s="21"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B104" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C104" s="23"/>
+      <c r="D104" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="E104" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="F104" s="21" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B105" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C105" s="23"/>
+      <c r="D105" s="26" t="s">
+        <v>405</v>
+      </c>
+      <c r="E105" s="21"/>
+      <c r="F105" s="21"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B106" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C106" s="23"/>
+      <c r="D106" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="E106" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F106" s="21" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B107" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C107" s="23"/>
+      <c r="D107" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E107" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="F107" s="21" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B108" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C108" s="23"/>
+      <c r="D108" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="E108" s="21"/>
+      <c r="F108" s="21"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B109" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="C109" s="23"/>
+      <c r="D109" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="E109" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="F109" s="21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B110" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="C110" s="23"/>
+      <c r="D110" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="E110" s="21"/>
+      <c r="F110" s="21"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B111" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="C111" s="23"/>
+      <c r="D111" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="E111" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="F111" s="21" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B112" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="C112" s="23"/>
+      <c r="D112" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="E112" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="F112" s="21" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B113" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="C113" s="23"/>
+      <c r="D113" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E113" s="21"/>
+      <c r="F113" s="21"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B114" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="C114" s="23"/>
+      <c r="D114" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="E114" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="F114" s="21" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B115" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="C115" s="23"/>
+      <c r="D115" s="26" t="s">
+        <v>397</v>
+      </c>
+      <c r="E115" s="21"/>
+      <c r="F115" s="21"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B116" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="C116" s="23"/>
+      <c r="D116" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="E116" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="F116" s="21" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B117" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="C117" s="23"/>
+      <c r="D117" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="E117" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="F117" s="21" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B118" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="C118" s="23"/>
+      <c r="D118" s="26" t="s">
+        <v>396</v>
+      </c>
+      <c r="E118" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="F118" s="21" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B119" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="D119" s="25" t="s">
+        <v>395</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD34E334-5291-47B3-A268-9B3E716C83AF}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1687,25 +4810,25 @@
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="7" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>5</v>
@@ -1717,7 +4840,7 @@
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -1731,17 +4854,17 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="7" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1749,7 +4872,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
@@ -1766,7 +4889,7 @@
         <v>42</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
@@ -1783,7 +4906,7 @@
         <v>43</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>5</v>
@@ -1800,7 +4923,7 @@
         <v>44</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>6</v>
@@ -1817,7 +4940,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>5</v>
@@ -1832,7 +4955,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>5</v>
@@ -1849,7 +4972,7 @@
         <v>46</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>5</v>
@@ -1864,7 +4987,7 @@
         <v>47</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>5</v>
@@ -1881,7 +5004,7 @@
         <v>48</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>6</v>
@@ -1898,7 +5021,7 @@
         <v>49</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>6</v>
@@ -1913,7 +5036,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>5</v>
@@ -1929,7 +5052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DB2B28-039E-4BD1-B89C-953EDD84E051}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1957,10 +5080,10 @@
         <v>22</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1976,12 +5099,10 @@
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>101</v>
-      </c>
+      <c r="E2" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="198" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -1997,10 +5118,266 @@
         <v>29</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E2:F2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBEC812-F90C-44E3-B962-AD2191B553DE}">
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="54.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2"/>
+    <col min="9" max="9" width="13.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="2"/>
+    <col min="11" max="11" width="5.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="14" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>100</v>
+      <c r="D8" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D10" s="11"/>
+    </row>
+    <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2009,116 +5386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBEC812-F90C-44E3-B962-AD2191B553DE}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="5.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="13.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="5.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55016CA4-31C4-4B3F-A4B6-EDEF5B983C20}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2148,13 +5416,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2162,7 +5430,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
@@ -2174,7 +5442,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -2185,122 +5453,122 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>

--- a/기획/림버스 컴퍼니/스킬 테이블.xlsx
+++ b/기획/림버스 컴퍼니/스킬 테이블.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\림버스 컴퍼니\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F03486C-7A51-498D-A996-345CF6F71083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A2DE29-B4FA-4DB2-9832-3B3D6DA63194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="360" windowWidth="28680" windowHeight="12600" tabRatio="796" activeTab="4" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
+    <workbookView xWindow="315" yWindow="480" windowWidth="18705" windowHeight="7170" tabRatio="796" firstSheet="2" activeTab="2" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
   </bookViews>
   <sheets>
-    <sheet name="테이블 링크" sheetId="11" r:id="rId1"/>
-    <sheet name="전투 스킬 메인 테이블" sheetId="1" r:id="rId2"/>
+    <sheet name="스킬 슬롯 링크 목록" sheetId="11" r:id="rId1"/>
+    <sheet name="스킬 메인 테이블" sheetId="1" r:id="rId2"/>
     <sheet name="스킬 효과 테이블" sheetId="6" r:id="rId3"/>
     <sheet name="코인 효과 테이블" sheetId="2" r:id="rId4"/>
     <sheet name="패시브 스킬 테이블" sheetId="10" r:id="rId5"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="441">
   <si>
     <t xml:space="preserve">한글명 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -325,10 +325,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>00-보유, 01-미보유, 02-미만, 03-이하, 04-동일, 05-이상, 06-초과, 07-N당</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬 ID 규칙 참조.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -385,10 +381,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Condition Keyword ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Condition Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -417,10 +409,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>조건 키워드 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>타임 키워드 ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -542,59 +530,6 @@
   </si>
   <si>
     <t>Result Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(+)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(+)00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -604,10 +539,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>순서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>번외 코드(메인 테이블 사용 X)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3059,14 +2990,6 @@
   </si>
   <si>
     <t>조건 세부 분류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조건 키워드 형식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Keyword Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3120,6 +3043,118 @@
 2X-일반 공격 2 스킬 계통
 3X-일반 공격 3 스킬 계통
 4X-일반 수비 스킬 계통</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-본인, 01-스킬 대상, 02-아군, 03-아군 전체, 04-적군, 05-적군 전체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 대상 키워드 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result Target Keyword ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소속 키워드 ID 목록 참조. 결과 대상(Result Target)항목의 값이 본인 및 스킬 대상일 경우 공백.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Keyword Target_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 키워드 대상_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 키워드 대상_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Keyword Target_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 대상 키워드 ID_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Target Keyword ID_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소속 키워드 ID 목록 참조. 조건 키워드 대상(Condition Target Keyword Target)항목의 값이 본인 및 스킬 대상일 경우 공백.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 대상 키워드 ID_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition Target Keyword ID_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 키워드 대상_3</t>
+  </si>
+  <si>
+    <t>Condition Keyword Target_3</t>
+  </si>
+  <si>
+    <t>00-본인, 01-스킬 대상, 02-아군, 03-아군 전체, 04-적군, 06-적군 전체</t>
+  </si>
+  <si>
+    <t>조건 대상 키워드 ID_3</t>
+  </si>
+  <si>
+    <t>Condition Target Keyword ID_3</t>
+  </si>
+  <si>
+    <t>조건 키워드 ID_3</t>
+  </si>
+  <si>
+    <t>Condition Keyword ID_3</t>
+  </si>
+  <si>
+    <t>조건 키워드 형식_3</t>
+  </si>
+  <si>
+    <t>Condition Keyword Type_3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(+)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3685,7 +3720,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
@@ -3699,7 +3734,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>5</v>
@@ -3708,37 +3743,37 @@
         <v>11</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -3783,13 +3818,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3797,7 +3832,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
@@ -3811,7 +3846,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -3828,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
@@ -3842,7 +3877,7 @@
         <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
@@ -3859,7 +3894,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>5</v>
@@ -3876,7 +3911,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>5</v>
@@ -3890,7 +3925,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>5</v>
@@ -3907,7 +3942,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>5</v>
@@ -3921,7 +3956,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>5</v>
@@ -3935,7 +3970,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>5</v>
@@ -3957,13 +3992,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14839D91-30A9-41E5-AB17-89F8A163A9E9}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="114.75" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3985,10 +4020,10 @@
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
@@ -3997,15 +4032,15 @@
         <v>11</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
@@ -4014,97 +4049,109 @@
         <v>11</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="7"/>
+      <c r="A4" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="26"/>
+      <c r="E4" s="7" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>70</v>
+        <v>426</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>427</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>11</v>
-      </c>
+      <c r="D5" s="26"/>
       <c r="E5" s="7" t="s">
-        <v>33</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="10" t="b">
+      <c r="D7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="D8" s="26"/>
       <c r="E8" s="7" t="s">
-        <v>33</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="b">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D9" s="26"/>
       <c r="E9" s="7" t="s">
-        <v>37</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>5</v>
@@ -4118,10 +4165,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>6</v>
@@ -4134,59 +4181,75 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="7"/>
+      <c r="A12" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="7" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>64</v>
+        <v>435</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="D13" s="26"/>
       <c r="E13" s="7" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="7"/>
+      <c r="A14" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>38</v>
+        <v>438</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>439</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="D15" s="26" t="b">
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>420</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>39</v>
+        <v>402</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>5</v>
@@ -4194,114 +4257,172 @@
       <c r="D16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="7"/>
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="D18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>41</v>
+        <v>416</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>417</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="2" t="b">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D19" s="26"/>
       <c r="E19" s="7" t="s">
-        <v>37</v>
+        <v>418</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>42</v>
+        <v>419</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>68</v>
+        <v>420</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="10" t="b">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D20" s="26"/>
       <c r="E20" s="7" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>422</v>
+      <c r="D21" s="2">
+        <v>0</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="7"/>
+      <c r="E25" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD34E334-5291-47B3-A268-9B3E716C83AF}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.5" customWidth="1"/>
+    <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.375" customWidth="1"/>
+    <col min="5" max="5" width="114.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -4323,10 +4444,10 @@
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
@@ -4335,15 +4456,15 @@
         <v>11</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>5</v>
@@ -4357,7 +4478,7 @@
         <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4371,10 +4492,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
@@ -4383,102 +4504,114 @@
         <v>11</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="7"/>
+      <c r="A6" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="7" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>70</v>
+        <v>426</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
+        <v>427</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>11</v>
-      </c>
+      <c r="D7" s="26"/>
       <c r="E7" s="7" t="s">
-        <v>33</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="10" t="b">
+      <c r="D9" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>11</v>
-      </c>
+      <c r="D10" s="26"/>
       <c r="E10" s="7" t="s">
-        <v>33</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="10" t="b">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D11" s="26"/>
       <c r="E11" s="7" t="s">
-        <v>37</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="26" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -4487,15 +4620,15 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="10" t="b">
+      <c r="D13" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -4503,142 +4636,422 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="7"/>
+      <c r="A14" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="7" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>64</v>
+        <v>435</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>34</v>
-      </c>
+      <c r="D15" s="26"/>
       <c r="E15" s="7" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="7"/>
+      <c r="A16" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>438</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>439</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>47</v>
+        <v>6</v>
+      </c>
+      <c r="D17" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>423</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>65</v>
+        <v>422</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="3"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="7" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="26"/>
+      <c r="E19" s="7" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>404</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>66</v>
+        <v>406</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>41</v>
+        <v>405</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>67</v>
+        <v>407</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="2" t="b">
+      <c r="D21" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>42</v>
+        <v>424</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>68</v>
+        <v>425</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>421</v>
+        <v>5</v>
+      </c>
+      <c r="D22" s="26"/>
+      <c r="E22" s="7" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>45</v>
+        <v>429</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>69</v>
+        <v>430</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="D23" s="26"/>
+      <c r="E23" s="7" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="26"/>
+      <c r="E26" s="7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="7" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="7" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="26"/>
+      <c r="E34" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="26">
+        <v>0</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>46</v>
       </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4676,13 +5089,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -4690,7 +5103,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
@@ -4702,7 +5115,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -4713,122 +5126,122 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>
@@ -4856,995 +5269,995 @@
   <sheetData>
     <row r="1" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="B1" s="23" t="s">
-        <v>204</v>
-      </c>
       <c r="C1" s="16" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D1" s="16"/>
       <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D6" s="20"/>
       <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>200</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>206</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="20"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="20"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D22" s="20"/>
       <c r="E22" s="20"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="20"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="20"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D26" s="20"/>
       <c r="E26" s="20"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="20"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D30" s="20"/>
       <c r="E30" s="20"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D31" s="20"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D32" s="20"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D33" s="20"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D34" s="20"/>
       <c r="E34" s="20"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D35" s="20"/>
       <c r="E35" s="20"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D36" s="20"/>
       <c r="E36" s="20"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D37" s="20"/>
       <c r="E37" s="20"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D38" s="20"/>
       <c r="E38" s="20"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D39" s="20"/>
       <c r="E39" s="20"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D44" s="20"/>
       <c r="E44" s="20"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D45" s="20"/>
       <c r="E45" s="20"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D46" s="20"/>
       <c r="E46" s="20"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D47" s="20"/>
       <c r="E47" s="20"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D48" s="20"/>
       <c r="E48" s="20"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D50" s="20"/>
       <c r="E50" s="20"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D53" s="20"/>
       <c r="E53" s="20"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D54" s="20"/>
       <c r="E54" s="20"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D55" s="20"/>
       <c r="E55" s="20"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D56" s="20"/>
       <c r="E56" s="20"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D58" s="20"/>
       <c r="E58" s="20"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D59" s="20"/>
       <c r="E59" s="20"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C60" s="25" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C61" s="24" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C63" s="24" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C69" s="24" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C72" s="24" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C77" s="20"/>
       <c r="D77" s="20"/>
@@ -5852,559 +6265,559 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C81" s="24" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B86" s="22" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B90" s="22" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B91" s="22" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B96" s="22" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C97" s="25" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B98" s="22" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B99" s="22" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D99" s="20"/>
       <c r="E99" s="20"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B100" s="22" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C100" s="24" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B101" s="22" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C101" s="24" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C102" s="24" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B103" s="22" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C103" s="24" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B104" s="22" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C104" s="24" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B105" s="22" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C105" s="24" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B106" s="22" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B107" s="22" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D107" s="20"/>
       <c r="E107" s="20"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C108" s="24" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D108" s="20"/>
       <c r="E108" s="20"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B109" s="22" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C109" s="24" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D109" s="20"/>
       <c r="E109" s="20"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B110" s="22" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D110" s="20"/>
       <c r="E110" s="20"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B111" s="22" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D111" s="20"/>
       <c r="E111" s="20"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B112" s="22" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D112" s="20"/>
       <c r="E112" s="20"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B113" s="22" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C113" s="24" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D113" s="20"/>
       <c r="E113" s="20"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C114" s="24" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D114" s="20"/>
       <c r="E114" s="20"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B115" s="22" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C115" s="24" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D115" s="20"/>
       <c r="E115" s="20"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C116" s="25" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D116" s="20"/>
       <c r="E116" s="20"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B117" s="22" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D117" s="20"/>
       <c r="E117" s="20"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B118" s="22" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C118" s="20" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D118" s="20"/>
       <c r="E118" s="20"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B119" s="22" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C119" s="25" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C120" s="24" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -6416,19 +6829,18 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DB2B28-039E-4BD1-B89C-953EDD84E051}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="28.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
@@ -6442,13 +6854,10 @@
         <v>22</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -6462,11 +6871,10 @@
         <v>25</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" s="26"/>
-    </row>
-    <row r="3" spans="1:6" ht="198" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="198" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
@@ -6477,19 +6885,13 @@
         <v>29</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E2:F2"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6518,228 +6920,228 @@
   <sheetData>
     <row r="1" spans="1:4" s="14" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11"/>
       <c r="B3" s="11" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11"/>
       <c r="B4" s="11" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11"/>
       <c r="B6" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11"/>
       <c r="B7" s="11" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11"/>
       <c r="B9" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11"/>
       <c r="B10" s="11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11"/>
       <c r="B14" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11"/>
       <c r="B15" s="11" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="11" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/기획/림버스 컴퍼니/스킬 테이블.xlsx
+++ b/기획/림버스 컴퍼니/스킬 테이블.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\림버스 컴퍼니\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A2DE29-B4FA-4DB2-9832-3B3D6DA63194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A28823-8B19-41D4-BCAC-821B1B45E5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="480" windowWidth="18705" windowHeight="7170" tabRatio="796" firstSheet="2" activeTab="2" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
+    <workbookView xWindow="-90" yWindow="45" windowWidth="18705" windowHeight="7830" tabRatio="841" firstSheet="2" activeTab="4" xr2:uid="{A86327C2-E956-496D-8858-F28C59A501C0}"/>
   </bookViews>
   <sheets>
     <sheet name="스킬 슬롯 링크 목록" sheetId="11" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="459">
   <si>
     <t xml:space="preserve">한글명 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -533,12 +533,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>mX-메인 효과
-cX-코인 효과
-X=순서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>번외 코드(메인 테이블 사용 X)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3023,14 +3017,6 @@
   </si>
   <si>
     <t>Condition Keyword Type_2</t>
-  </si>
-  <si>
-    <t>00-조건 없음, 01-미보유, 02-미만, 03-이하, 04-동일, 05-이상, 06-초과, 07-N당</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>false-감소, true-증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>00</t>
@@ -3054,22 +3040,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>00-본인, 01-스킬 대상, 02-아군, 03-아군 전체, 04-적군, 05-적군 전체</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>결과 대상 키워드 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result Target Keyword ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>소속 키워드 ID 목록 참조. 결과 대상(Result Target)항목의 값이 본인 및 스킬 대상일 경우 공백.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Condition Keyword Target_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3086,41 +3056,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>조건 대상 키워드 ID_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Target Keyword ID_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>소속 키워드 ID 목록 참조. 조건 키워드 대상(Condition Target Keyword Target)항목의 값이 본인 및 스킬 대상일 경우 공백.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조건 대상 키워드 ID_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Condition Target Keyword ID_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>조건 키워드 대상_3</t>
   </si>
   <si>
     <t>Condition Keyword Target_3</t>
   </si>
   <si>
-    <t>00-본인, 01-스킬 대상, 02-아군, 03-아군 전체, 04-적군, 06-적군 전체</t>
-  </si>
-  <si>
-    <t>조건 대상 키워드 ID_3</t>
-  </si>
-  <si>
-    <t>Condition Target Keyword ID_3</t>
-  </si>
-  <si>
     <t>조건 키워드 ID_3</t>
   </si>
   <si>
@@ -3155,6 +3096,258 @@
       </rPr>
       <t>00</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bk24</t>
+  </si>
+  <si>
+    <t>가중치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>altm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상시 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 만족 시 상시 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok37</t>
+  </si>
+  <si>
+    <t>뇌운</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뇌기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뇌기 잠식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광폭화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ok38</t>
+  </si>
+  <si>
+    <t>ok39</t>
+  </si>
+  <si>
+    <t>ok40</t>
+  </si>
+  <si>
+    <t>00-조건 없음, 01-미보유, 02-미만, 03-이하, 04-동일, 05-이상, 06-초과, 07-N당, 08-보유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최종 위력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bk25</t>
+  </si>
+  <si>
+    <r>
+      <t>스킬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 사용 전</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용 전 슬롯에서 적용</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-본인, 01-스킬 대상, 02-아군, 03-적군, 04-해당 스킬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00-본인, 01-스킬 대상, 02-아군, 03-적군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gk50</t>
+  </si>
+  <si>
+    <t>false-감소 또는 미분류, true-증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변경 결과 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chage Result ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-메인 효과
+C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">-코인 효과
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=순서</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>코인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 재사용</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gk51</t>
+  </si>
+  <si>
+    <t>gk52</t>
+  </si>
+  <si>
+    <t>스킬 피해량의 N% 피해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마지막 코인 피해량의 N% 피해</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3162,7 +3355,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3253,6 +3446,27 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="돋움"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3291,7 +3505,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3372,6 +3586,18 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3688,7 +3914,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A58AF3-DFBE-42DA-94BA-1C8D3714BF72}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="19.125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.25" style="1" bestFit="1" customWidth="1"/>
@@ -3698,7 +3924,7 @@
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3715,7 +3941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" s="3" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -3729,7 +3955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" s="3" customFormat="1">
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
@@ -3746,7 +3972,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" s="3" customFormat="1">
       <c r="A4" s="3" t="s">
         <v>71</v>
       </c>
@@ -3761,7 +3987,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" s="3" customFormat="1">
       <c r="A8" s="3" t="s">
         <v>48</v>
       </c>
@@ -3786,7 +4012,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBEBB1C6-45A4-4CCC-B8BB-4A16F0A92775}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="24.125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5" style="3" bestFit="1" customWidth="1"/>
@@ -3796,7 +4022,7 @@
     <col min="6" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3813,7 +4039,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
@@ -3827,7 +4053,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -3841,7 +4067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -3858,7 +4084,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -3872,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -3889,7 +4115,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
@@ -3906,7 +4132,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
@@ -3920,7 +4146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -3937,7 +4163,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -3951,7 +4177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -3965,7 +4191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
@@ -3979,10 +4205,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="E13" s="7"/>
     </row>
-    <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:5" ht="16.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3992,8 +4218,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14839D91-30A9-41E5-AB17-89F8A163A9E9}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.125" bestFit="1" customWidth="1"/>
@@ -4001,7 +4227,7 @@
     <col min="5" max="5" width="114.75" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="3" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4018,7 +4244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" s="3" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>71</v>
       </c>
@@ -4035,7 +4261,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
@@ -4052,37 +4278,39 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="26"/>
       <c r="E4" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="26"/>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E5" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>404</v>
       </c>
@@ -4090,321 +4318,270 @@
         <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="26"/>
+      <c r="E7" s="7" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>424</v>
-      </c>
       <c r="B8" s="3" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="26"/>
+      <c r="D8" s="10" t="s">
+        <v>11</v>
+      </c>
       <c r="E8" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="26"/>
+        <v>6</v>
+      </c>
+      <c r="D9" s="10" t="b">
+        <v>0</v>
+      </c>
       <c r="E9" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="7" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="C11" s="3" t="s">
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="10" t="b">
+      <c r="D12" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="7" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>435</v>
+        <v>62</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="26"/>
+      <c r="D13" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E13" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>436</v>
+        <v>38</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>437</v>
+        <v>61</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>11</v>
+      <c r="D14" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>438</v>
+        <v>39</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>439</v>
+        <v>63</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>62</v>
+        <v>414</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="D16" s="26"/>
       <c r="E16" s="7" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>34</v>
+      <c r="D17" s="2">
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>416</v>
+        <v>42</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>417</v>
+        <v>66</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="26"/>
+        <v>6</v>
+      </c>
+      <c r="D19" s="10" t="b">
+        <v>0</v>
+      </c>
       <c r="E19" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>419</v>
+        <v>45</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>420</v>
+        <v>67</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="26"/>
+      <c r="D20" s="2" t="s">
+        <v>411</v>
+      </c>
       <c r="E20" s="7" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>41</v>
+        <v>451</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>65</v>
+        <v>452</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="7"/>
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4415,8 +4592,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD34E334-5291-47B3-A268-9B3E716C83AF}">
-  <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.125" bestFit="1" customWidth="1"/>
@@ -4425,7 +4602,7 @@
     <col min="5" max="5" width="114.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4442,7 +4619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" s="3" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>48</v>
       </c>
@@ -4459,7 +4636,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" s="3" customFormat="1">
       <c r="A3" s="3" t="s">
         <v>73</v>
       </c>
@@ -4473,7 +4650,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -4490,7 +4667,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>68</v>
       </c>
@@ -4507,37 +4684,39 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="26"/>
+      <c r="D7" s="26" t="s">
+        <v>11</v>
+      </c>
       <c r="E7" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>404</v>
       </c>
@@ -4545,213 +4724,217 @@
         <v>406</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="26"/>
+      <c r="E9" s="7" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>424</v>
-      </c>
       <c r="B10" s="3" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="26"/>
+      <c r="D10" s="26" t="s">
+        <v>11</v>
+      </c>
       <c r="E10" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="26"/>
+        <v>6</v>
+      </c>
+      <c r="D11" s="26" t="b">
+        <v>0</v>
+      </c>
       <c r="E11" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="26"/>
+      <c r="E12" s="7" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="C13" s="3" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="26" t="b">
+      <c r="D14" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="7" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>435</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="26"/>
+      <c r="D15" s="26" t="s">
+        <v>34</v>
+      </c>
       <c r="E15" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>436</v>
+        <v>38</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>437</v>
+        <v>61</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>438</v>
+        <v>39</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>439</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="26"/>
       <c r="E18" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>426</v>
+        <v>40</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>427</v>
+        <v>64</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="26"/>
+      <c r="D19" s="26">
+        <v>0</v>
+      </c>
       <c r="E19" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>404</v>
+        <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>406</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="D20" s="26" t="b">
+        <v>0</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>405</v>
+        <v>42</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>407</v>
+        <v>66</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>6</v>
@@ -4760,298 +4943,40 @@
         <v>0</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>424</v>
+        <v>45</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>425</v>
+        <v>67</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="26"/>
+      <c r="D22" s="26" t="s">
+        <v>411</v>
+      </c>
       <c r="E22" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>429</v>
+        <v>97</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>430</v>
+        <v>98</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="26"/>
-      <c r="E23" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="7" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="26"/>
-      <c r="E27" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="26" t="s">
+      <c r="D23" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="7"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="7" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="26">
-        <v>0</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E39" s="7"/>
+      <c r="E23" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5062,7 +4987,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55016CA4-31C4-4B3F-A4B6-EDEF5B983C20}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -5070,7 +4995,7 @@
     <col min="4" max="4" width="139.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5084,7 +5009,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
@@ -5098,7 +5023,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -5110,7 +5035,7 @@
       </c>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -5124,7 +5049,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>77</v>
       </c>
@@ -5138,7 +5063,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
         <v>79</v>
       </c>
@@ -5152,7 +5077,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>80</v>
       </c>
@@ -5166,7 +5091,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>81</v>
       </c>
@@ -5180,7 +5105,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>82</v>
       </c>
@@ -5194,7 +5119,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
         <v>83</v>
       </c>
@@ -5208,7 +5133,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>84</v>
       </c>
@@ -5222,7 +5147,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
         <v>85</v>
       </c>
@@ -5236,7 +5161,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>95</v>
       </c>
@@ -5256,1409 +5181,1409 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06EC02D0-4C2D-408B-8AFB-DBB6E17830DA}">
-  <dimension ref="A1:E120"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E129"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="18" customWidth="1"/>
-    <col min="3" max="3" width="26.5" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.5" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.25" style="21" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.625" style="21" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="17" customFormat="1">
       <c r="A1" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="16"/>
       <c r="E1" s="16"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D6" s="20"/>
       <c r="E6" s="20"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="20"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="20"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D22" s="20"/>
       <c r="E22" s="20"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="20"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="20"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D26" s="20"/>
       <c r="E26" s="20"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="20"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D30" s="20"/>
       <c r="E30" s="20"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" s="20"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" s="20"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="D33" s="20"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="D34" s="20"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="D35" s="20"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>312</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="D31" s="20"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="D32" s="20"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="B33" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="C33" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="D33" s="20"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>178</v>
+      <c r="C36" s="24" t="s">
+        <v>225</v>
       </c>
       <c r="D36" s="20"/>
       <c r="E36" s="20"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>318</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>227</v>
+        <v>315</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>215</v>
       </c>
       <c r="D37" s="20"/>
       <c r="E37" s="20"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>319</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>228</v>
+        <v>316</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>177</v>
       </c>
       <c r="D38" s="20"/>
       <c r="E38" s="20"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>229</v>
+        <v>317</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>226</v>
       </c>
       <c r="D39" s="20"/>
       <c r="E39" s="20"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>179</v>
+        <v>319</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>228</v>
       </c>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>231</v>
+        <v>320</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>229</v>
       </c>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>232</v>
+        <v>321</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>178</v>
       </c>
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>233</v>
+        <v>322</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>230</v>
       </c>
       <c r="D44" s="20"/>
       <c r="E44" s="20"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D45" s="20"/>
       <c r="E45" s="20"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D46" s="20"/>
       <c r="E46" s="20"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>236</v>
+        <v>325</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>233</v>
       </c>
       <c r="D47" s="20"/>
       <c r="E47" s="20"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5">
       <c r="A48" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>180</v>
+        <v>326</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>234</v>
       </c>
       <c r="D48" s="20"/>
       <c r="E48" s="20"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>330</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>181</v>
+        <v>327</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>235</v>
       </c>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D50" s="20"/>
       <c r="E50" s="20"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>237</v>
+        <v>329</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>180</v>
       </c>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>333</v>
-      </c>
-      <c r="C52" s="25" t="s">
-        <v>238</v>
+        <v>330</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>181</v>
       </c>
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="A53" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="C53" s="25" t="s">
-        <v>239</v>
+        <v>331</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>236</v>
       </c>
       <c r="D53" s="20"/>
       <c r="E53" s="20"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>240</v>
+        <v>332</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>237</v>
       </c>
       <c r="D54" s="20"/>
       <c r="E54" s="20"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5">
       <c r="A55" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D55" s="20"/>
       <c r="E55" s="20"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5">
       <c r="A56" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C56" s="25" t="s">
-        <v>242</v>
+        <v>334</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>239</v>
       </c>
       <c r="D56" s="20"/>
       <c r="E56" s="20"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5">
       <c r="A57" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>338</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>215</v>
+        <v>335</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>240</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5">
       <c r="A58" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D58" s="20"/>
       <c r="E58" s="20"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5">
       <c r="A59" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>340</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>244</v>
+        <v>337</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>214</v>
       </c>
       <c r="D59" s="20"/>
       <c r="E59" s="20"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C60" s="25" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5">
       <c r="A61" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>246</v>
+        <v>339</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>243</v>
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5">
       <c r="A62" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>343</v>
-      </c>
-      <c r="C62" s="24" t="s">
-        <v>247</v>
+        <v>340</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>244</v>
       </c>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5">
       <c r="A63" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C63" s="24" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5">
       <c r="A64" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>249</v>
+        <v>342</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>246</v>
       </c>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5">
       <c r="A65" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="C65" s="25" t="s">
-        <v>250</v>
+        <v>343</v>
+      </c>
+      <c r="C65" s="24" t="s">
+        <v>247</v>
       </c>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5">
       <c r="A66" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5">
       <c r="A67" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5">
       <c r="A68" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>349</v>
-      </c>
-      <c r="C68" s="24" t="s">
-        <v>253</v>
+        <v>346</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>250</v>
       </c>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5">
       <c r="A69" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>350</v>
-      </c>
-      <c r="C69" s="24" t="s">
-        <v>254</v>
+        <v>347</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>251</v>
       </c>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5">
       <c r="A70" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5">
       <c r="A71" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="C71" s="25" t="s">
-        <v>256</v>
+        <v>349</v>
+      </c>
+      <c r="C71" s="24" t="s">
+        <v>253</v>
       </c>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5">
       <c r="A72" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C72" s="24" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5">
       <c r="A73" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5">
       <c r="A74" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="C74" s="20" t="s">
-        <v>183</v>
+        <v>352</v>
+      </c>
+      <c r="C74" s="24" t="s">
+        <v>256</v>
       </c>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5">
       <c r="A75" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="C75" s="20" t="s">
-        <v>184</v>
+        <v>353</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>257</v>
       </c>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5">
       <c r="A76" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5">
       <c r="A77" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>358</v>
-      </c>
-      <c r="C77" s="20"/>
+        <v>355</v>
+      </c>
+      <c r="C77" s="20" t="s">
+        <v>183</v>
+      </c>
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5">
       <c r="A78" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>359</v>
-      </c>
-      <c r="C78" s="24" t="s">
-        <v>259</v>
+        <v>356</v>
+      </c>
+      <c r="C78" s="20" t="s">
+        <v>184</v>
       </c>
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5">
       <c r="A79" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>360</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>260</v>
+        <v>357</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>454</v>
       </c>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5">
       <c r="A80" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>361</v>
-      </c>
-      <c r="C80" s="20" t="s">
-        <v>186</v>
+        <v>358</v>
+      </c>
+      <c r="C80" s="24" t="s">
+        <v>258</v>
       </c>
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5">
       <c r="A81" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="C81" s="24" t="s">
-        <v>261</v>
+        <v>359</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>259</v>
       </c>
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5">
       <c r="A82" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>363</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>262</v>
+        <v>360</v>
+      </c>
+      <c r="C82" s="20" t="s">
+        <v>185</v>
       </c>
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5">
       <c r="A83" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5">
       <c r="A84" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5">
       <c r="A85" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5">
       <c r="A86" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B86" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="C86" s="25" t="s">
-        <v>266</v>
+        <v>449</v>
+      </c>
+      <c r="C86" s="24" t="s">
+        <v>448</v>
       </c>
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5">
       <c r="A87" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>368</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>267</v>
+        <v>455</v>
+      </c>
+      <c r="C87" s="24" t="s">
+        <v>457</v>
       </c>
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5">
       <c r="A88" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>369</v>
+        <v>456</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>268</v>
+        <v>458</v>
       </c>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5">
       <c r="A89" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>370</v>
-      </c>
-      <c r="C89" s="25" t="s">
-        <v>269</v>
+        <v>364</v>
+      </c>
+      <c r="C89" s="24" t="s">
+        <v>263</v>
       </c>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5">
       <c r="A90" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B90" s="22" t="s">
-        <v>371</v>
-      </c>
-      <c r="C90" s="25" t="s">
-        <v>270</v>
+        <v>365</v>
+      </c>
+      <c r="C90" s="24" t="s">
+        <v>264</v>
       </c>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5">
       <c r="A91" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B91" s="22" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5">
       <c r="A92" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>373</v>
-      </c>
-      <c r="C92" s="20" t="s">
-        <v>187</v>
+        <v>367</v>
+      </c>
+      <c r="C92" s="25" t="s">
+        <v>266</v>
       </c>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5">
       <c r="A93" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>374</v>
-      </c>
-      <c r="C93" s="20" t="s">
-        <v>188</v>
+        <v>368</v>
+      </c>
+      <c r="C93" s="24" t="s">
+        <v>267</v>
       </c>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5">
       <c r="A94" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>375</v>
-      </c>
-      <c r="C94" s="24" t="s">
-        <v>272</v>
+        <v>369</v>
+      </c>
+      <c r="C94" s="25" t="s">
+        <v>268</v>
       </c>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5">
       <c r="A95" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5">
       <c r="A96" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B96" s="22" t="s">
-        <v>377</v>
-      </c>
-      <c r="C96" s="24" t="s">
-        <v>274</v>
+        <v>371</v>
+      </c>
+      <c r="C96" s="25" t="s">
+        <v>270</v>
       </c>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5">
       <c r="A97" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>378</v>
-      </c>
-      <c r="C97" s="25" t="s">
-        <v>275</v>
+        <v>372</v>
+      </c>
+      <c r="C97" s="20" t="s">
+        <v>186</v>
       </c>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5">
       <c r="A98" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B98" s="22" t="s">
-        <v>379</v>
-      </c>
-      <c r="C98" s="24" t="s">
-        <v>276</v>
+        <v>373</v>
+      </c>
+      <c r="C98" s="20" t="s">
+        <v>187</v>
       </c>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5">
       <c r="A99" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B99" s="22" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D99" s="20"/>
       <c r="E99" s="20"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5">
       <c r="A100" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B100" s="22" t="s">
-        <v>381</v>
-      </c>
-      <c r="C100" s="24" t="s">
-        <v>278</v>
+        <v>375</v>
+      </c>
+      <c r="C100" s="25" t="s">
+        <v>272</v>
       </c>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5">
       <c r="A101" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B101" s="22" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C101" s="24" t="s">
-        <v>219</v>
+        <v>273</v>
       </c>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5">
       <c r="A102" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>383</v>
-      </c>
-      <c r="C102" s="24" t="s">
-        <v>218</v>
+        <v>377</v>
+      </c>
+      <c r="C102" s="25" t="s">
+        <v>274</v>
       </c>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5">
       <c r="A103" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B103" s="22" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C103" s="24" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5">
       <c r="A104" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B104" s="22" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C104" s="24" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5">
       <c r="A105" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B105" s="22" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C105" s="24" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5">
       <c r="A106" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B106" s="22" t="s">
-        <v>387</v>
-      </c>
-      <c r="C106" s="25" t="s">
-        <v>281</v>
+        <v>381</v>
+      </c>
+      <c r="C106" s="24" t="s">
+        <v>218</v>
       </c>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5">
       <c r="A107" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B107" s="22" t="s">
-        <v>388</v>
-      </c>
-      <c r="C107" s="25" t="s">
-        <v>282</v>
+        <v>382</v>
+      </c>
+      <c r="C107" s="24" t="s">
+        <v>217</v>
       </c>
       <c r="D107" s="20"/>
       <c r="E107" s="20"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5">
       <c r="A108" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C108" s="24" t="s">
         <v>216</v>
@@ -6666,158 +6591,267 @@
       <c r="D108" s="20"/>
       <c r="E108" s="20"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5">
       <c r="A109" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B109" s="22" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C109" s="24" t="s">
-        <v>215</v>
+        <v>278</v>
       </c>
       <c r="D109" s="20"/>
       <c r="E109" s="20"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5">
       <c r="A110" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B110" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="C110" s="25" t="s">
-        <v>214</v>
+        <v>385</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>279</v>
       </c>
       <c r="D110" s="20"/>
       <c r="E110" s="20"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5">
       <c r="A111" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B111" s="22" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>213</v>
+        <v>280</v>
       </c>
       <c r="D111" s="20"/>
       <c r="E111" s="20"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5">
       <c r="A112" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B112" s="22" t="s">
-        <v>393</v>
-      </c>
-      <c r="C112" s="20" t="s">
-        <v>189</v>
+        <v>387</v>
+      </c>
+      <c r="C112" s="25" t="s">
+        <v>281</v>
       </c>
       <c r="D112" s="20"/>
       <c r="E112" s="20"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5">
       <c r="A113" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B113" s="22" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C113" s="24" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D113" s="20"/>
       <c r="E113" s="20"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5">
       <c r="A114" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C114" s="24" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D114" s="20"/>
       <c r="E114" s="20"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5">
       <c r="A115" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B115" s="22" t="s">
-        <v>396</v>
-      </c>
-      <c r="C115" s="24" t="s">
-        <v>210</v>
+        <v>390</v>
+      </c>
+      <c r="C115" s="25" t="s">
+        <v>213</v>
       </c>
       <c r="D115" s="20"/>
       <c r="E115" s="20"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5">
       <c r="A116" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C116" s="25" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D116" s="20"/>
       <c r="E116" s="20"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5">
       <c r="A117" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B117" s="22" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D117" s="20"/>
       <c r="E117" s="20"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5">
       <c r="A118" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B118" s="22" t="s">
-        <v>399</v>
-      </c>
-      <c r="C118" s="20" t="s">
-        <v>191</v>
+        <v>393</v>
+      </c>
+      <c r="C118" s="24" t="s">
+        <v>211</v>
       </c>
       <c r="D118" s="20"/>
       <c r="E118" s="20"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5">
       <c r="A119" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B119" s="22" t="s">
-        <v>400</v>
-      </c>
-      <c r="C119" s="25" t="s">
-        <v>208</v>
+        <v>394</v>
+      </c>
+      <c r="C119" s="24" t="s">
+        <v>210</v>
       </c>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5">
       <c r="A120" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C120" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="D120" s="20"/>
+      <c r="E120" s="20"/>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B121" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="C121" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="D121" s="20"/>
+      <c r="E121" s="20"/>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B122" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="C122" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D122" s="20"/>
+      <c r="E122" s="20"/>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B123" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="C123" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D123" s="20"/>
+      <c r="E123" s="20"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B124" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="C124" s="25" t="s">
         <v>207</v>
+      </c>
+      <c r="D124" s="20"/>
+      <c r="E124" s="20"/>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B125" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="C125" s="24" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B126" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="C126" s="21" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B127" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="C127" s="21" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B128" s="22" t="s">
+        <v>438</v>
+      </c>
+      <c r="C128" s="21" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B129" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="C129" s="21" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -6830,7 +6864,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DB2B28-039E-4BD1-B89C-953EDD84E051}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="14.375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="2" bestFit="1" customWidth="1"/>
@@ -6840,7 +6874,7 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
@@ -6854,10 +6888,10 @@
         <v>22</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -6871,10 +6905,10 @@
         <v>25</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="198" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="198">
       <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
@@ -6885,10 +6919,10 @@
         <v>29</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>99</v>
+        <v>412</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -6900,8 +6934,8 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBEC812-F90C-44E3-B962-AD2191B553DE}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.5" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="2" customWidth="1"/>
@@ -6918,230 +6952,256 @@
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="14" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="14" customFormat="1" ht="17.25" thickBot="1">
       <c r="A1" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="D1" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="28" customFormat="1" ht="17.25" thickBot="1">
+      <c r="A2" s="27" t="s">
+        <v>428</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="C3" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:4" ht="17.25" thickBot="1">
       <c r="A4" s="11"/>
       <c r="B4" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:4" s="26" customFormat="1" ht="17.25" thickBot="1">
       <c r="A6" s="11"/>
       <c r="B6" s="11" t="s">
-        <v>145</v>
+        <v>444</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A7" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:4" ht="17.25" thickBot="1">
       <c r="A9" s="11"/>
       <c r="B9" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A10" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="B10" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="17.25" thickBot="1">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>139</v>
+        <v>147</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>124</v>
-      </c>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" spans="1:4" ht="17.25" thickBot="1">
       <c r="A13" s="11"/>
       <c r="B13" s="11" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A14" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>126</v>
+      <c r="C14" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="17.25" thickBot="1">
       <c r="A15" s="11"/>
       <c r="B15" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>130</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A16" s="11"/>
       <c r="B16" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="17.25" thickBot="1">
       <c r="A17" s="11"/>
       <c r="B17" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A20" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
+      <c r="C20" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18" s="11" t="s">
+      <c r="D20" s="11" t="s">
         <v>136</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
